--- a/data/almacen.xlsx
+++ b/data/almacen.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Productos" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Movimientos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Reportes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,12 +41,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001b5e20"/>
+        <bgColor rgb="001b5e20"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -53,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -427,52 +443,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Unidad de Medida</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Fecha de Creación</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>URL Imagen</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Stock Actual</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Unidad Medida</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Fecha Creación</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>URL Imagen</t>
         </is>
       </c>
     </row>
@@ -487,82 +518,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID Movimiento</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>ID Producto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre Producto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Stock Anterior</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Stock Nuevo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Fecha</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de Reporte</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total Productos</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Mes</t>
+          <t>Total Movimientos</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ID Producto</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Nombre Producto</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Stock Anterior</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Stock Nuevo</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Motivo</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
+          <t>Stock Total Valor</t>
         </is>
       </c>
     </row>

--- a/data/almacen.xlsx
+++ b/data/almacen.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -43,12 +43,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001b5e20"/>
         <bgColor rgb="001b5e20"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,12 +64,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -443,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -456,54 +447,39 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unidad de Medida</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Fecha de Creación</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>URL Imagen</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Stock Actual</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Unidad Medida</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Fecha Creación</t>
         </is>
       </c>
     </row>
